--- a/db/A7XLK-1404-WebInformation.xlsx
+++ b/db/A7XLK-1404-WebInformation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D91655-B834-4040-9150-720E6A44BE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05192D7-DF89-DD46-BE9C-7F095EC53C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11700" yWindow="4820" windowWidth="28260" windowHeight="17560" xr2:uid="{2B2AD4FA-9B91-2346-8F8C-40168F957E39}"/>
+    <workbookView xWindow="-31020" yWindow="7060" windowWidth="28260" windowHeight="17560" xr2:uid="{2B2AD4FA-9B91-2346-8F8C-40168F957E39}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>

--- a/db/A7XLK-1404-WebInformation.xlsx
+++ b/db/A7XLK-1404-WebInformation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05192D7-DF89-DD46-BE9C-7F095EC53C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2405A48F-38A6-8B4F-B48A-011C3B9E3B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31020" yWindow="7060" windowWidth="28260" windowHeight="17560" xr2:uid="{2B2AD4FA-9B91-2346-8F8C-40168F957E39}"/>
+    <workbookView xWindow="6640" yWindow="2500" windowWidth="28260" windowHeight="17560" xr2:uid="{2B2AD4FA-9B91-2346-8F8C-40168F957E39}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="170">
   <si>
     <t>No</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -697,6 +697,22 @@
   </si>
   <si>
     <t>生活查詢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>408</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-408.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tgos.tw/tgos/Web/Address/TGOS_Address.aspx?fbclid=IwAR2Y2QtTuEYl3uACZLVuKsCnHcCj7Y301aApNkc3tJIUZLl7H8956P4gpu0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>門牌定位服務</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1104,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A0CB41-3B89-4349-A7FC-75FA2EC3F206}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -1716,27 +1732,27 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>119</v>
+        <v>89</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>121</v>
+        <v>167</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>118</v>
@@ -1745,18 +1761,18 @@
         <v>118</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>118</v>
@@ -1765,18 +1781,18 @@
         <v>118</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>118</v>
@@ -1785,18 +1801,18 @@
         <v>118</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>118</v>
@@ -1805,18 +1821,18 @@
         <v>118</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>118</v>
@@ -1825,18 +1841,18 @@
         <v>118</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>118</v>
@@ -1845,18 +1861,18 @@
         <v>118</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>118</v>
@@ -1864,19 +1880,19 @@
       <c r="C38" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>147</v>
+      <c r="D38" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>118</v>
@@ -1885,12 +1901,32 @@
         <v>118</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>153</v>
       </c>
     </row>
@@ -1915,17 +1951,18 @@
     <hyperlink ref="F26" r:id="rId16" xr:uid="{810A3255-50FD-5846-89F5-03055B67E370}"/>
     <hyperlink ref="F27" r:id="rId17" xr:uid="{3DC272CA-8A60-0648-AA1C-2BE59A9C73DF}"/>
     <hyperlink ref="F28" r:id="rId18" xr:uid="{D7E5799B-768A-CC43-9B48-A4A92C6DDE5E}"/>
-    <hyperlink ref="F32" r:id="rId19" xr:uid="{53F2F752-C82A-CD45-AD49-6CA09F608218}"/>
-    <hyperlink ref="F33" r:id="rId20" xr:uid="{A13BA009-2E93-6547-A515-E1F52BF5EA01}"/>
-    <hyperlink ref="F34" r:id="rId21" xr:uid="{0E4BCF35-6B78-FC42-AC3E-6922E652FAF7}"/>
-    <hyperlink ref="F35" r:id="rId22" xr:uid="{74EBAFFA-96FA-5F47-9230-BD310329D6AB}"/>
-    <hyperlink ref="F36" r:id="rId23" xr:uid="{6A73115C-E7C2-C54A-8A9B-DDE734225534}"/>
+    <hyperlink ref="F33" r:id="rId19" xr:uid="{53F2F752-C82A-CD45-AD49-6CA09F608218}"/>
+    <hyperlink ref="F34" r:id="rId20" xr:uid="{A13BA009-2E93-6547-A515-E1F52BF5EA01}"/>
+    <hyperlink ref="F35" r:id="rId21" xr:uid="{0E4BCF35-6B78-FC42-AC3E-6922E652FAF7}"/>
+    <hyperlink ref="F36" r:id="rId22" xr:uid="{74EBAFFA-96FA-5F47-9230-BD310329D6AB}"/>
+    <hyperlink ref="F37" r:id="rId23" xr:uid="{6A73115C-E7C2-C54A-8A9B-DDE734225534}"/>
     <hyperlink ref="F13" r:id="rId24" xr:uid="{A62553A9-53B8-C840-8C16-D47923C7E3CF}"/>
     <hyperlink ref="F23" r:id="rId25" xr:uid="{65544D7F-5359-8945-A089-6E47C0F0E247}"/>
     <hyperlink ref="F30" r:id="rId26" xr:uid="{A0110837-CF23-124A-AAA2-EF66C624126C}"/>
-    <hyperlink ref="F37" r:id="rId27" xr:uid="{59FCD997-C119-5545-8178-5021D0F65A14}"/>
-    <hyperlink ref="F38" r:id="rId28" xr:uid="{9AF90005-FB2C-714E-B429-C60EFCD5BA99}"/>
-    <hyperlink ref="F39" r:id="rId29" xr:uid="{17976D58-E4B9-D542-BEBE-3196CAD21665}"/>
+    <hyperlink ref="F38" r:id="rId27" xr:uid="{59FCD997-C119-5545-8178-5021D0F65A14}"/>
+    <hyperlink ref="F39" r:id="rId28" xr:uid="{9AF90005-FB2C-714E-B429-C60EFCD5BA99}"/>
+    <hyperlink ref="F40" r:id="rId29" xr:uid="{17976D58-E4B9-D542-BEBE-3196CAD21665}"/>
+    <hyperlink ref="F31" r:id="rId30" xr:uid="{596548C5-C447-8D47-BB18-BB0F47DB6CF7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1404-WebInformation.xlsx
+++ b/db/A7XLK-1404-WebInformation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2405A48F-38A6-8B4F-B48A-011C3B9E3B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75358836-742D-4541-B297-5C0E3314FE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6640" yWindow="2500" windowWidth="28260" windowHeight="17560" xr2:uid="{2B2AD4FA-9B91-2346-8F8C-40168F957E39}"/>
+    <workbookView xWindow="5000" yWindow="3500" windowWidth="27860" windowHeight="16820" xr2:uid="{392F8878-2F2B-2849-AD01-EEB5E8317FAF}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="174">
   <si>
     <t>No</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>Category1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Category</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -57,115 +61,119 @@
   </si>
   <si>
     <t>101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>行車資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>交通資訊</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>每週油價查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-101.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://m.gas.goodlife.tw/gas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>國道即時路況</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-102.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://1968.freeway.gov.tw/n_speed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>103</t>
   </si>
   <si>
     <t>加油位址資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-103.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.google.com/maps/d/edit?mid=1KjxHpFnLbtTVEeJhan-_xLJSaLTb1tKw&amp;usp=sharing</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>104</t>
   </si>
   <si>
     <t>全國道路救援</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-104.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://towingnet.com.tw/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>201</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>大眾交通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>台鐵時刻查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-201.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.railway.gov.tw/tra-tip-web/tip/tip001/tip112/gobytime</t>
   </si>
   <si>
     <t>202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>高鐵時刻查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-202.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.thsrc.com.tw/ArticleContent/a3b630bb-1066-4352-a1ef-58c7b4e8ef7c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>203</t>
   </si>
   <si>
     <t>台北捷運資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-203.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://m.metro.taipei/</t>
@@ -175,107 +183,146 @@
   </si>
   <si>
     <t>桃園捷運資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-204.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.tymetro.com.tw/tymetro-new/tw/_pages/travel-guide/timetable-search.php</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>205</t>
   </si>
   <si>
     <t>大台北公車動態</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-205.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://ebus.gov.taipei/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>206</t>
   </si>
   <si>
     <t>桃園公車動態</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-206.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://ebus.tycg.gov.tw/NewTaoyuan/Dybus.aspx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>207</t>
   </si>
   <si>
     <t>YouBike站點</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-207.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://tycg.youbike.com.tw/station/map?_id=5cb7e421083e7b42664b87e2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>601</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>政府繳費</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>路邊停車繳費</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-601.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://epark.tycg.gov.tw/public/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>602</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>汽機車燃料費</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-602.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.mvdis.gov.tw/m3-emv-fee/fee/fuelFee</t>
   </si>
   <si>
     <t>301</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>生活資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活查詢</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>樂透彩劵開獎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-301.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>http://lotto2.arclink.com.tw/649/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>302</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>當日股市查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-302.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://tw.stock.yahoo.com/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>303</t>
   </si>
   <si>
     <t>統一發票兌獎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-303.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.etax.nat.gov.tw/etw-main/web/ETW183W1/</t>
@@ -285,56 +332,81 @@
   </si>
   <si>
     <t>在地即時影像</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-304.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://tw.live/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>305</t>
   </si>
   <si>
     <t>天氣資訊查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-305.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.cwb.gov.tw/V8/C/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>310</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>颱風動向Windy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.windy.com/?24.989,121.318,5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>306</t>
   </si>
   <si>
     <t>地籍資訊查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-306.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://easymap.land.moi.gov.tw/P02/Index</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>307</t>
   </si>
   <si>
     <t>房屋實價查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-307.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://market.591.com.tw/?refid=4&amp;gclid=Cj0KCQiAw_H-BRD-ARIsALQE_2NR1hr1mPPAfoyWGVaAIM_FL5036x8H5Fq_33pSGv66m97xxieLO_caAvlxEALw_wcB</t>
@@ -344,122 +416,122 @@
   </si>
   <si>
     <t>當季菜價查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-308.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.twfood.cc/vege?page=2</t>
   </si>
   <si>
     <t>309</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>空氣品質監測</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-309.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://airtw.epa.gov.tw/CHT/EnvMonitoring/Local/LocalMonitoring.aspx?Type=EPB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>401</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>查詢工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>郵遞區號查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-401.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.post.gov.tw/post/internet/SearchZone/index.jsp?ID=130107</t>
   </si>
   <si>
     <t>402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>英文地址翻譯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-402.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.post.gov.tw/post/internet/Postal/index.jsp?ID=207</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>403</t>
   </si>
   <si>
     <t>貨幣換算工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-403.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://tw.exchange-rates.org/converter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>404</t>
   </si>
   <si>
     <t>網速即時查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-404.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://fast.com/zh/tw/#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>405</t>
   </si>
   <si>
     <t>勞保給付試算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-405.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.bli.gov.tw/0014162.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>406</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>單位換算查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-406.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://toolbxs.com/zh-TW/converter/unit</t>
@@ -469,124 +541,140 @@
   </si>
   <si>
     <t>DesignEvo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-407.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.designevo.com/tw/logo-maker/" title="免費線上logo製作軟體</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>408</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>門牌定位服務</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-408.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tgos.tw/tgos/Web/Address/TGOS_Address.aspx?fbclid=IwAR2Y2QtTuEYl3uACZLVuKsCnHcCj7Y301aApNkc3tJIUZLl7H8956P4gpu0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>501</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>娛樂資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>上映電影查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-501.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://movies.yahoo.com.tw/showtimes</t>
   </si>
   <si>
     <t>502</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>連續劇熱播表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-502.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://kan.sogou.com/top/dianshiju/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>503</t>
   </si>
   <si>
     <t>附近景點快搜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-503.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.taiwan.net.tw/m1.aspx?sNo=0000064</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>504</t>
   </si>
   <si>
     <t>主題旅遊資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-504.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.taiwan.net.tw/m1.aspx?sNo=0000108</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>505</t>
   </si>
   <si>
     <t>藝文活動資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-505.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://event.moc.gov.tw/mp.asp?mp=1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>506</t>
   </si>
   <si>
     <t>地區節慶活動</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-506.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.taiwan.net.tw/m1.aspx?sNo=0000104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>507</t>
   </si>
   <si>
     <t>智慧導遊-桃園</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-507.jpg</t>
   </si>
   <si>
     <t>https://tcwang.github.io/TravelGuide-Taoyuan/index.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>508</t>
@@ -611,14 +699,14 @@
       </rPr>
       <t>-花東</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-508.jpg</t>
   </si>
   <si>
     <t>https://tcwang.github.io/TravelGuide-EastCoast/index.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>509</t>
@@ -643,77 +731,18 @@
       </rPr>
       <t>-離島</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-509.jpg</t>
   </si>
   <si>
     <t>https://tcwang.github.io/TravelGuide-Islands/Index.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>601</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>政府繳費</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>路邊停車繳費</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-601.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://epark.tycg.gov.tw/public/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>602</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>汽機車燃料費</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-602.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.mvdis.gov.tw/m3-emv-fee/fee/fuelFee</t>
-  </si>
-  <si>
-    <t>Category1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>交通資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生活查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>408</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-408.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.tgos.tw/tgos/Web/Address/TGOS_Address.aspx?fbclid=IwAR2Y2QtTuEYl3uACZLVuKsCnHcCj7Y301aApNkc3tJIUZLl7H8956P4gpu0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>門牌定位服務</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-310.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -724,13 +753,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -750,6 +772,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -793,7 +822,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -801,9 +830,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1119,8 +1148,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A0CB41-3B89-4349-A7FC-75FA2EC3F206}">
-  <dimension ref="A1:F40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73074AA-F564-AD47-9C34-8D0E67223CF3}">
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -1135,834 +1164,855 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>164</v>
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>164</v>
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>164</v>
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>164</v>
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>164</v>
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>164</v>
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>164</v>
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>164</v>
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>164</v>
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>164</v>
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>164</v>
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>164</v>
+        <v>54</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>158</v>
+        <v>56</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>164</v>
+        <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>53</v>
+        <v>63</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>165</v>
+        <v>63</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>165</v>
+        <v>63</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>165</v>
+        <v>63</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>165</v>
+        <v>63</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>75</v>
+        <v>173</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>165</v>
+        <v>63</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>165</v>
+        <v>63</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>165</v>
+        <v>63</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>165</v>
+        <v>63</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>104</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>165</v>
+        <v>104</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>165</v>
+        <v>104</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>165</v>
+        <v>104</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>165</v>
+        <v>104</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>165</v>
+        <v>104</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>169</v>
+        <v>104</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>168</v>
+        <v>130</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>119</v>
+        <v>104</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>121</v>
+        <v>134</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>145</v>
+        <v>159</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>147</v>
+        <v>137</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>153</v>
+        <v>167</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{6E8B1BA1-F2D1-4846-8282-1085D229E084}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{137F4075-32E5-A047-87CC-CEFF6D58D273}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{5A558F81-AFAA-204F-93E8-F93D4959B1E5}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{1E916376-481B-6143-9289-983786C5896F}"/>
-    <hyperlink ref="F7" r:id="rId5" xr:uid="{D7811FB9-FE8A-644A-995A-292E924D5BED}"/>
-    <hyperlink ref="F12" r:id="rId6" xr:uid="{689DE542-8171-7A41-8029-29277A4E8146}"/>
-    <hyperlink ref="F10" r:id="rId7" xr:uid="{B7A41C4F-F2AD-4942-A41E-232EB944675D}"/>
-    <hyperlink ref="F9" r:id="rId8" xr:uid="{7F658EC8-F6AA-E244-9106-4CA4F3E6D9F5}"/>
-    <hyperlink ref="F11" r:id="rId9" xr:uid="{D407D309-1B25-AA48-AEF3-0304DA627F5A}"/>
-    <hyperlink ref="F15" r:id="rId10" xr:uid="{1D425BAB-A3E3-C047-8C2D-C573F0422064}"/>
-    <hyperlink ref="F16" r:id="rId11" xr:uid="{6748EEF8-61AF-DB4C-A5CC-5FF4A8D95399}"/>
-    <hyperlink ref="F18" r:id="rId12" xr:uid="{56FCE03A-9E75-2A47-B9F1-52F87E038D10}"/>
-    <hyperlink ref="F19" r:id="rId13" xr:uid="{0922670E-D3EA-4A48-A0BA-F2ED85C06070}"/>
-    <hyperlink ref="F20" r:id="rId14" xr:uid="{6DCD0C52-52AD-154E-B195-17D8B5CA56F5}"/>
-    <hyperlink ref="F25" r:id="rId15" xr:uid="{0A1A4060-68FB-1042-8173-057E3C641676}"/>
-    <hyperlink ref="F26" r:id="rId16" xr:uid="{810A3255-50FD-5846-89F5-03055B67E370}"/>
-    <hyperlink ref="F27" r:id="rId17" xr:uid="{3DC272CA-8A60-0648-AA1C-2BE59A9C73DF}"/>
-    <hyperlink ref="F28" r:id="rId18" xr:uid="{D7E5799B-768A-CC43-9B48-A4A92C6DDE5E}"/>
-    <hyperlink ref="F33" r:id="rId19" xr:uid="{53F2F752-C82A-CD45-AD49-6CA09F608218}"/>
-    <hyperlink ref="F34" r:id="rId20" xr:uid="{A13BA009-2E93-6547-A515-E1F52BF5EA01}"/>
-    <hyperlink ref="F35" r:id="rId21" xr:uid="{0E4BCF35-6B78-FC42-AC3E-6922E652FAF7}"/>
-    <hyperlink ref="F36" r:id="rId22" xr:uid="{74EBAFFA-96FA-5F47-9230-BD310329D6AB}"/>
-    <hyperlink ref="F37" r:id="rId23" xr:uid="{6A73115C-E7C2-C54A-8A9B-DDE734225534}"/>
-    <hyperlink ref="F13" r:id="rId24" xr:uid="{A62553A9-53B8-C840-8C16-D47923C7E3CF}"/>
-    <hyperlink ref="F23" r:id="rId25" xr:uid="{65544D7F-5359-8945-A089-6E47C0F0E247}"/>
-    <hyperlink ref="F30" r:id="rId26" xr:uid="{A0110837-CF23-124A-AAA2-EF66C624126C}"/>
-    <hyperlink ref="F38" r:id="rId27" xr:uid="{59FCD997-C119-5545-8178-5021D0F65A14}"/>
-    <hyperlink ref="F39" r:id="rId28" xr:uid="{9AF90005-FB2C-714E-B429-C60EFCD5BA99}"/>
-    <hyperlink ref="F40" r:id="rId29" xr:uid="{17976D58-E4B9-D542-BEBE-3196CAD21665}"/>
-    <hyperlink ref="F31" r:id="rId30" xr:uid="{596548C5-C447-8D47-BB18-BB0F47DB6CF7}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{BAA7D95C-6E1A-8F48-8FE7-D2CE1D46802D}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{361ABFA0-65A4-914E-BD0F-DF3377C0C3AB}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{2EB97F1B-948F-004F-A053-CD30DCF44E29}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{2110EB8D-A46B-D046-8C07-4D1F28C4E9ED}"/>
+    <hyperlink ref="F7" r:id="rId5" xr:uid="{33227F7A-229B-8947-B37F-D6A4659EB47C}"/>
+    <hyperlink ref="F12" r:id="rId6" xr:uid="{716339FC-7F12-EA48-9995-7C474D0320D0}"/>
+    <hyperlink ref="F10" r:id="rId7" xr:uid="{F779899C-3F73-3440-A492-1C66F2B620C7}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{65E521B8-6489-7540-A0B8-ABFC65A2BE99}"/>
+    <hyperlink ref="F11" r:id="rId9" xr:uid="{F14F0F5B-995D-B842-8E4F-1355DFB26170}"/>
+    <hyperlink ref="F15" r:id="rId10" xr:uid="{5000AC10-E9A7-2F48-A2E1-A708430E8FD3}"/>
+    <hyperlink ref="F16" r:id="rId11" xr:uid="{EB22B113-4D72-7647-BB12-A4CDD0E84D0D}"/>
+    <hyperlink ref="F18" r:id="rId12" xr:uid="{522AE814-B103-F34F-9D64-872658CD9973}"/>
+    <hyperlink ref="F19" r:id="rId13" xr:uid="{9647D01F-922A-FD4A-9DDD-5190A1432D17}"/>
+    <hyperlink ref="F21" r:id="rId14" xr:uid="{3ABB1380-024B-F845-A7B5-2AF547CFDE2E}"/>
+    <hyperlink ref="F26" r:id="rId15" xr:uid="{A65C8833-7044-4445-9794-215739B5ADAB}"/>
+    <hyperlink ref="F27" r:id="rId16" xr:uid="{F654D832-5868-E74B-AC72-556BE69299C9}"/>
+    <hyperlink ref="F28" r:id="rId17" xr:uid="{4E4EC6F8-E6E4-D54B-8AA8-5FE15BF5A751}"/>
+    <hyperlink ref="F29" r:id="rId18" xr:uid="{9765A227-82C2-D549-9458-DDC2D3C28D8D}"/>
+    <hyperlink ref="F34" r:id="rId19" xr:uid="{CD3DA3AB-30AB-524E-9120-1075FCEB7656}"/>
+    <hyperlink ref="F35" r:id="rId20" xr:uid="{77D5314A-0EBE-4B47-B3B2-F976C9B41794}"/>
+    <hyperlink ref="F36" r:id="rId21" xr:uid="{CD171E9C-3BA1-2541-8ED8-7E8ADE5E0BBD}"/>
+    <hyperlink ref="F37" r:id="rId22" xr:uid="{066093EC-3EC4-5349-B64C-CAA4B3AD38C2}"/>
+    <hyperlink ref="F38" r:id="rId23" xr:uid="{1B7909EB-3D00-C942-AAE7-00B7E5D828CD}"/>
+    <hyperlink ref="F13" r:id="rId24" xr:uid="{752C52CB-FC5F-B447-84E0-E36801D34DA7}"/>
+    <hyperlink ref="F24" r:id="rId25" xr:uid="{6FFCA69B-21A4-CB47-9C03-B94CB60F3CB0}"/>
+    <hyperlink ref="F31" r:id="rId26" xr:uid="{18492F93-4F5D-E54F-8131-EF4E56BB3753}"/>
+    <hyperlink ref="F39" r:id="rId27" xr:uid="{89CB1C70-DE0E-E64D-B256-D814AA226C99}"/>
+    <hyperlink ref="F40" r:id="rId28" xr:uid="{04F522F7-AD32-DC45-8F1B-7192EBEF625A}"/>
+    <hyperlink ref="F41" r:id="rId29" xr:uid="{72BD642C-EE89-8946-AF0A-11CAD94A0C95}"/>
+    <hyperlink ref="F32" r:id="rId30" xr:uid="{D72923EF-ED37-F140-B006-2328C3703B41}"/>
+    <hyperlink ref="F20" r:id="rId31" xr:uid="{D2F469D1-1983-AD4A-A51E-2E275AEAB5B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1404-WebInformation.xlsx
+++ b/db/A7XLK-1404-WebInformation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75358836-742D-4541-B297-5C0E3314FE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E74BB6A-AA1E-654D-8FAA-CDB1DECADF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5000" yWindow="3500" windowWidth="27860" windowHeight="16820" xr2:uid="{392F8878-2F2B-2849-AD01-EEB5E8317FAF}"/>
+    <workbookView xWindow="7580" yWindow="2260" windowWidth="27860" windowHeight="16820" xr2:uid="{392F8878-2F2B-2849-AD01-EEB5E8317FAF}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="185">
   <si>
     <t>No</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -742,6 +742,50 @@
   </si>
   <si>
     <t>fig/AiCity-945-WebInformation-310.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>果汁排行榜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://guozhivip.com/rank/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-果汁排行榜.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>311</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>大數據導航</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://hao.199it.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-大數據導航.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>312</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>懶盤搜索</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-lzpan.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://lzpan.com/</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1149,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73074AA-F564-AD47-9C34-8D0E67223CF3}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -1441,7 +1485,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>62</v>
+        <v>181</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>63</v>
@@ -1449,19 +1493,19 @@
       <c r="C15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>65</v>
+      <c r="D15" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>67</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>63</v>
@@ -1470,18 +1514,18 @@
         <v>64</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>71</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>63</v>
@@ -1490,18 +1534,18 @@
         <v>64</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>75</v>
+        <v>176</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>63</v>
@@ -1509,19 +1553,19 @@
       <c r="C18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>77</v>
+      <c r="D18" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>63</v>
@@ -1530,18 +1574,18 @@
         <v>64</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>63</v>
@@ -1550,18 +1594,18 @@
         <v>64</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>63</v>
@@ -1570,18 +1614,18 @@
         <v>64</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>63</v>
@@ -1590,18 +1634,18 @@
         <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>63</v>
@@ -1610,18 +1654,18 @@
         <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>98</v>
+        <v>173</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>63</v>
@@ -1630,78 +1674,78 @@
         <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>111</v>
+        <v>97</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>104</v>
@@ -1710,18 +1754,18 @@
         <v>64</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>119</v>
+        <v>106</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>104</v>
@@ -1730,18 +1774,18 @@
         <v>64</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>104</v>
@@ -1750,18 +1794,18 @@
         <v>64</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>104</v>
@@ -1770,18 +1814,18 @@
         <v>64</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>104</v>
@@ -1789,79 +1833,79 @@
       <c r="C32" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>133</v>
+      <c r="D32" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>137</v>
+        <v>104</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>137</v>
+        <v>104</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>146</v>
+        <v>104</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>137</v>
@@ -1870,18 +1914,18 @@
         <v>137</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>152</v>
+        <v>139</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>137</v>
@@ -1890,18 +1934,18 @@
         <v>137</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>137</v>
@@ -1910,18 +1954,18 @@
         <v>137</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>137</v>
@@ -1930,18 +1974,18 @@
         <v>137</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>137</v>
@@ -1949,19 +1993,19 @@
       <c r="C40" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>166</v>
+      <c r="D40" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>137</v>
@@ -1969,13 +2013,73 @@
       <c r="C41" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1991,28 +2095,31 @@
     <hyperlink ref="F10" r:id="rId7" xr:uid="{F779899C-3F73-3440-A492-1C66F2B620C7}"/>
     <hyperlink ref="F9" r:id="rId8" xr:uid="{65E521B8-6489-7540-A0B8-ABFC65A2BE99}"/>
     <hyperlink ref="F11" r:id="rId9" xr:uid="{F14F0F5B-995D-B842-8E4F-1355DFB26170}"/>
-    <hyperlink ref="F15" r:id="rId10" xr:uid="{5000AC10-E9A7-2F48-A2E1-A708430E8FD3}"/>
-    <hyperlink ref="F16" r:id="rId11" xr:uid="{EB22B113-4D72-7647-BB12-A4CDD0E84D0D}"/>
-    <hyperlink ref="F18" r:id="rId12" xr:uid="{522AE814-B103-F34F-9D64-872658CD9973}"/>
-    <hyperlink ref="F19" r:id="rId13" xr:uid="{9647D01F-922A-FD4A-9DDD-5190A1432D17}"/>
-    <hyperlink ref="F21" r:id="rId14" xr:uid="{3ABB1380-024B-F845-A7B5-2AF547CFDE2E}"/>
-    <hyperlink ref="F26" r:id="rId15" xr:uid="{A65C8833-7044-4445-9794-215739B5ADAB}"/>
-    <hyperlink ref="F27" r:id="rId16" xr:uid="{F654D832-5868-E74B-AC72-556BE69299C9}"/>
-    <hyperlink ref="F28" r:id="rId17" xr:uid="{4E4EC6F8-E6E4-D54B-8AA8-5FE15BF5A751}"/>
-    <hyperlink ref="F29" r:id="rId18" xr:uid="{9765A227-82C2-D549-9458-DDC2D3C28D8D}"/>
-    <hyperlink ref="F34" r:id="rId19" xr:uid="{CD3DA3AB-30AB-524E-9120-1075FCEB7656}"/>
-    <hyperlink ref="F35" r:id="rId20" xr:uid="{77D5314A-0EBE-4B47-B3B2-F976C9B41794}"/>
-    <hyperlink ref="F36" r:id="rId21" xr:uid="{CD171E9C-3BA1-2541-8ED8-7E8ADE5E0BBD}"/>
-    <hyperlink ref="F37" r:id="rId22" xr:uid="{066093EC-3EC4-5349-B64C-CAA4B3AD38C2}"/>
-    <hyperlink ref="F38" r:id="rId23" xr:uid="{1B7909EB-3D00-C942-AAE7-00B7E5D828CD}"/>
+    <hyperlink ref="F18" r:id="rId10" xr:uid="{5000AC10-E9A7-2F48-A2E1-A708430E8FD3}"/>
+    <hyperlink ref="F19" r:id="rId11" xr:uid="{EB22B113-4D72-7647-BB12-A4CDD0E84D0D}"/>
+    <hyperlink ref="F21" r:id="rId12" xr:uid="{522AE814-B103-F34F-9D64-872658CD9973}"/>
+    <hyperlink ref="F22" r:id="rId13" xr:uid="{9647D01F-922A-FD4A-9DDD-5190A1432D17}"/>
+    <hyperlink ref="F24" r:id="rId14" xr:uid="{3ABB1380-024B-F845-A7B5-2AF547CFDE2E}"/>
+    <hyperlink ref="F29" r:id="rId15" xr:uid="{A65C8833-7044-4445-9794-215739B5ADAB}"/>
+    <hyperlink ref="F30" r:id="rId16" xr:uid="{F654D832-5868-E74B-AC72-556BE69299C9}"/>
+    <hyperlink ref="F31" r:id="rId17" xr:uid="{4E4EC6F8-E6E4-D54B-8AA8-5FE15BF5A751}"/>
+    <hyperlink ref="F32" r:id="rId18" xr:uid="{9765A227-82C2-D549-9458-DDC2D3C28D8D}"/>
+    <hyperlink ref="F37" r:id="rId19" xr:uid="{CD3DA3AB-30AB-524E-9120-1075FCEB7656}"/>
+    <hyperlink ref="F38" r:id="rId20" xr:uid="{77D5314A-0EBE-4B47-B3B2-F976C9B41794}"/>
+    <hyperlink ref="F39" r:id="rId21" xr:uid="{CD171E9C-3BA1-2541-8ED8-7E8ADE5E0BBD}"/>
+    <hyperlink ref="F40" r:id="rId22" xr:uid="{066093EC-3EC4-5349-B64C-CAA4B3AD38C2}"/>
+    <hyperlink ref="F41" r:id="rId23" xr:uid="{1B7909EB-3D00-C942-AAE7-00B7E5D828CD}"/>
     <hyperlink ref="F13" r:id="rId24" xr:uid="{752C52CB-FC5F-B447-84E0-E36801D34DA7}"/>
-    <hyperlink ref="F24" r:id="rId25" xr:uid="{6FFCA69B-21A4-CB47-9C03-B94CB60F3CB0}"/>
-    <hyperlink ref="F31" r:id="rId26" xr:uid="{18492F93-4F5D-E54F-8131-EF4E56BB3753}"/>
-    <hyperlink ref="F39" r:id="rId27" xr:uid="{89CB1C70-DE0E-E64D-B256-D814AA226C99}"/>
-    <hyperlink ref="F40" r:id="rId28" xr:uid="{04F522F7-AD32-DC45-8F1B-7192EBEF625A}"/>
-    <hyperlink ref="F41" r:id="rId29" xr:uid="{72BD642C-EE89-8946-AF0A-11CAD94A0C95}"/>
-    <hyperlink ref="F32" r:id="rId30" xr:uid="{D72923EF-ED37-F140-B006-2328C3703B41}"/>
-    <hyperlink ref="F20" r:id="rId31" xr:uid="{D2F469D1-1983-AD4A-A51E-2E275AEAB5B9}"/>
+    <hyperlink ref="F27" r:id="rId25" xr:uid="{6FFCA69B-21A4-CB47-9C03-B94CB60F3CB0}"/>
+    <hyperlink ref="F34" r:id="rId26" xr:uid="{18492F93-4F5D-E54F-8131-EF4E56BB3753}"/>
+    <hyperlink ref="F42" r:id="rId27" xr:uid="{89CB1C70-DE0E-E64D-B256-D814AA226C99}"/>
+    <hyperlink ref="F43" r:id="rId28" xr:uid="{04F522F7-AD32-DC45-8F1B-7192EBEF625A}"/>
+    <hyperlink ref="F44" r:id="rId29" xr:uid="{72BD642C-EE89-8946-AF0A-11CAD94A0C95}"/>
+    <hyperlink ref="F35" r:id="rId30" xr:uid="{D72923EF-ED37-F140-B006-2328C3703B41}"/>
+    <hyperlink ref="F23" r:id="rId31" xr:uid="{D2F469D1-1983-AD4A-A51E-2E275AEAB5B9}"/>
+    <hyperlink ref="F17" r:id="rId32" xr:uid="{6508207D-BBE9-CA4B-829A-334E053A7F40}"/>
+    <hyperlink ref="F16" r:id="rId33" xr:uid="{48BBCC1A-D008-C145-8EA7-2A1C9A10CFCB}"/>
+    <hyperlink ref="F15" r:id="rId34" xr:uid="{A4A1607A-2169-D04B-A519-2CC1E57426DC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1404-WebInformation.xlsx
+++ b/db/A7XLK-1404-WebInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E74BB6A-AA1E-654D-8FAA-CDB1DECADF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A000314D-3ED9-7C40-8954-1CF6008EB445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7580" yWindow="2260" windowWidth="27860" windowHeight="16820" xr2:uid="{392F8878-2F2B-2849-AD01-EEB5E8317FAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="185">
   <si>
     <t>No</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -769,10 +769,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>fig/XLK-1401-News/XLK-142-大數據導航.jpeg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>312</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -786,6 +782,10 @@
   </si>
   <si>
     <t>https://lzpan.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-大數據導航.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1508,7 +1508,7 @@
         <v>177</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>64</v>
@@ -1517,7 +1517,7 @@
         <v>178</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>179</v>
@@ -1528,7 +1528,7 @@
         <v>84</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>64</v>
@@ -1747,9 +1747,6 @@
       <c r="A28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C28" s="2" t="s">
         <v>64</v>
       </c>
@@ -1767,9 +1764,6 @@
       <c r="A29" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C29" s="2" t="s">
         <v>64</v>
       </c>
@@ -1786,9 +1780,6 @@
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>64</v>

--- a/db/A7XLK-1404-WebInformation.xlsx
+++ b/db/A7XLK-1404-WebInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A000314D-3ED9-7C40-8954-1CF6008EB445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD654CD-6F68-1347-8F80-FCACE26BC8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7580" yWindow="2260" windowWidth="27860" windowHeight="16820" xr2:uid="{392F8878-2F2B-2849-AD01-EEB5E8317FAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="201">
   <si>
     <t>No</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -788,12 +788,99 @@
     <t>fig/XLK-1401-News/XLK-142-大數據導航.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>075</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>影貓電影</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-MVCAT.png</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.mvcat.com/</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>072</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>劇迷 Gimy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-劇迷.png</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>073</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>中國人線上看</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-1401-News/XLK-142-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>中國人線上看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://chinaq.biz/cn/</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>071</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>美國電視頻道</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/AiCity-923-USTVGo.jpeg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ustvgo.tv/</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -844,6 +931,13 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="PMingLiU"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -870,7 +964,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -878,6 +972,9 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1193,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73074AA-F564-AD47-9C34-8D0E67223CF3}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -1747,6 +1844,9 @@
       <c r="A28" s="1" t="s">
         <v>103</v>
       </c>
+      <c r="B28" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="C28" s="2" t="s">
         <v>64</v>
       </c>
@@ -1764,6 +1864,9 @@
       <c r="A29" s="1" t="s">
         <v>108</v>
       </c>
+      <c r="B29" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="C29" s="2" t="s">
         <v>64</v>
       </c>
@@ -1781,6 +1884,9 @@
       <c r="A30" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="B30" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="C30" s="2" t="s">
         <v>64</v>
       </c>
@@ -1894,9 +2000,9 @@
         <v>135</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="1" t="s">
-        <v>136</v>
+    <row r="36" spans="1:6" s="6" customFormat="1">
+      <c r="A36" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>137</v>
@@ -1904,19 +2010,19 @@
       <c r="C36" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="1" t="s">
-        <v>141</v>
+      <c r="D36" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" s="6" customFormat="1">
+      <c r="A37" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>137</v>
@@ -1924,19 +2030,19 @@
       <c r="C37" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="1" t="s">
-        <v>145</v>
+      <c r="D37" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" s="6" customFormat="1">
+      <c r="A38" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>137</v>
@@ -1944,19 +2050,19 @@
       <c r="C38" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="1" t="s">
-        <v>149</v>
+      <c r="D38" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" s="6" customFormat="1">
+      <c r="A39" s="5" t="s">
+        <v>197</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>137</v>
@@ -1964,19 +2070,19 @@
       <c r="C39" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>152</v>
+      <c r="D39" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>137</v>
@@ -1985,18 +2091,18 @@
         <v>137</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>156</v>
+        <v>139</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>137</v>
@@ -2005,18 +2111,18 @@
         <v>137</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>137</v>
@@ -2025,18 +2131,18 @@
         <v>137</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>137</v>
@@ -2044,33 +2150,113 @@
       <c r="C43" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>166</v>
+      <c r="D43" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="B48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F48" s="3" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2095,22 +2281,26 @@
     <hyperlink ref="F30" r:id="rId16" xr:uid="{F654D832-5868-E74B-AC72-556BE69299C9}"/>
     <hyperlink ref="F31" r:id="rId17" xr:uid="{4E4EC6F8-E6E4-D54B-8AA8-5FE15BF5A751}"/>
     <hyperlink ref="F32" r:id="rId18" xr:uid="{9765A227-82C2-D549-9458-DDC2D3C28D8D}"/>
-    <hyperlink ref="F37" r:id="rId19" xr:uid="{CD3DA3AB-30AB-524E-9120-1075FCEB7656}"/>
-    <hyperlink ref="F38" r:id="rId20" xr:uid="{77D5314A-0EBE-4B47-B3B2-F976C9B41794}"/>
-    <hyperlink ref="F39" r:id="rId21" xr:uid="{CD171E9C-3BA1-2541-8ED8-7E8ADE5E0BBD}"/>
-    <hyperlink ref="F40" r:id="rId22" xr:uid="{066093EC-3EC4-5349-B64C-CAA4B3AD38C2}"/>
-    <hyperlink ref="F41" r:id="rId23" xr:uid="{1B7909EB-3D00-C942-AAE7-00B7E5D828CD}"/>
+    <hyperlink ref="F41" r:id="rId19" xr:uid="{CD3DA3AB-30AB-524E-9120-1075FCEB7656}"/>
+    <hyperlink ref="F42" r:id="rId20" xr:uid="{77D5314A-0EBE-4B47-B3B2-F976C9B41794}"/>
+    <hyperlink ref="F43" r:id="rId21" xr:uid="{CD171E9C-3BA1-2541-8ED8-7E8ADE5E0BBD}"/>
+    <hyperlink ref="F44" r:id="rId22" xr:uid="{066093EC-3EC4-5349-B64C-CAA4B3AD38C2}"/>
+    <hyperlink ref="F45" r:id="rId23" xr:uid="{1B7909EB-3D00-C942-AAE7-00B7E5D828CD}"/>
     <hyperlink ref="F13" r:id="rId24" xr:uid="{752C52CB-FC5F-B447-84E0-E36801D34DA7}"/>
     <hyperlink ref="F27" r:id="rId25" xr:uid="{6FFCA69B-21A4-CB47-9C03-B94CB60F3CB0}"/>
     <hyperlink ref="F34" r:id="rId26" xr:uid="{18492F93-4F5D-E54F-8131-EF4E56BB3753}"/>
-    <hyperlink ref="F42" r:id="rId27" xr:uid="{89CB1C70-DE0E-E64D-B256-D814AA226C99}"/>
-    <hyperlink ref="F43" r:id="rId28" xr:uid="{04F522F7-AD32-DC45-8F1B-7192EBEF625A}"/>
-    <hyperlink ref="F44" r:id="rId29" xr:uid="{72BD642C-EE89-8946-AF0A-11CAD94A0C95}"/>
+    <hyperlink ref="F46" r:id="rId27" xr:uid="{89CB1C70-DE0E-E64D-B256-D814AA226C99}"/>
+    <hyperlink ref="F47" r:id="rId28" xr:uid="{04F522F7-AD32-DC45-8F1B-7192EBEF625A}"/>
+    <hyperlink ref="F48" r:id="rId29" xr:uid="{72BD642C-EE89-8946-AF0A-11CAD94A0C95}"/>
     <hyperlink ref="F35" r:id="rId30" xr:uid="{D72923EF-ED37-F140-B006-2328C3703B41}"/>
     <hyperlink ref="F23" r:id="rId31" xr:uid="{D2F469D1-1983-AD4A-A51E-2E275AEAB5B9}"/>
     <hyperlink ref="F17" r:id="rId32" xr:uid="{6508207D-BBE9-CA4B-829A-334E053A7F40}"/>
     <hyperlink ref="F16" r:id="rId33" xr:uid="{48BBCC1A-D008-C145-8EA7-2A1C9A10CFCB}"/>
     <hyperlink ref="F15" r:id="rId34" xr:uid="{A4A1607A-2169-D04B-A519-2CC1E57426DC}"/>
+    <hyperlink ref="F39" r:id="rId35" xr:uid="{A9B76A01-5C69-2042-B892-8A6CCA8FA194}"/>
+    <hyperlink ref="F37" r:id="rId36" xr:uid="{BC59EB1D-78B5-4541-AFA6-9F643F390499}"/>
+    <hyperlink ref="F38" r:id="rId37" xr:uid="{DCAAB2E2-2A00-E241-934E-979AE7E30648}"/>
+    <hyperlink ref="F36" r:id="rId38" xr:uid="{F00BAE17-5761-C048-9157-F06361A501DD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1404-WebInformation.xlsx
+++ b/db/A7XLK-1404-WebInformation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD654CD-6F68-1347-8F80-FCACE26BC8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E1C508B-EB7B-BC4F-B04E-A99F1E58C459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7580" yWindow="2260" windowWidth="27860" windowHeight="16820" xr2:uid="{392F8878-2F2B-2849-AD01-EEB5E8317FAF}"/>
+    <workbookView xWindow="8780" yWindow="10020" windowWidth="27860" windowHeight="16820" xr2:uid="{28C80269-29E6-DF43-8891-366D5E15C1BF}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="225">
   <si>
     <t>No</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -274,6 +274,195 @@
     <t>https://www.mvdis.gov.tw/m3-emv-fee/fee/fuelFee</t>
   </si>
   <si>
+    <t>313</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>查詢工具</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活查詢</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>軟體下載 FossHub</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-313.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.fosshub.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>314</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>格式轉換 Aconvert</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-314.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.aconvert.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>心智圖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> GitMind</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-315.jpeg</t>
+  </si>
+  <si>
+    <t>https://gitmind.com/tw/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <r>
+      <t>肌肉訓練 MuscleWiki</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-316.jpeg</t>
+  </si>
+  <si>
+    <t>https://musclewiki.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <r>
+      <t>音樂下載 SoundCloud</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-317.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://soundcloud.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>瀏覽加速器 SpeedyFox</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-318.jpeg</t>
+  </si>
+  <si>
+    <t>https://crystalidea.com/speedyfox</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>312</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>懶盤搜索</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-lzpan.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://lzpan.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>311</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>大數據導航</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-大數據導航.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://hao.199it.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>310</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>果汁排行榜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-果汁排行榜.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://guozhivip.com/rank/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>301</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -282,10 +471,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>生活查詢</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>樂透彩劵開獎</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -355,10 +540,6 @@
   </si>
   <si>
     <t>https://www.cwb.gov.tw/V8/C/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>310</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -379,6 +560,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>fig/AiCity-945-WebInformation-310.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>https://www.windy.com/?24.989,121.318,5</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -446,10 +631,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>查詢工具</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>郵遞區號查詢</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -565,232 +746,15 @@
   </si>
   <si>
     <t>https://www.tgos.tw/tgos/Web/Address/TGOS_Address.aspx?fbclid=IwAR2Y2QtTuEYl3uACZLVuKsCnHcCj7Y301aApNkc3tJIUZLl7H8956P4gpu0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>501</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>娛樂資訊</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>上映電影查詢</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-501.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://movies.yahoo.com.tw/showtimes</t>
-  </si>
-  <si>
-    <t>502</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>連續劇熱播表</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-502.jpeg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://kan.sogou.com/top/dianshiju/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>503</t>
-  </si>
-  <si>
-    <t>附近景點快搜</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-503.jpeg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.taiwan.net.tw/m1.aspx?sNo=0000064</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>504</t>
-  </si>
-  <si>
-    <t>主題旅遊資訊</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-504.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.taiwan.net.tw/m1.aspx?sNo=0000108</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>505</t>
-  </si>
-  <si>
-    <t>藝文活動資訊</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-505.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://event.moc.gov.tw/mp.asp?mp=1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>506</t>
-  </si>
-  <si>
-    <t>地區節慶活動</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-506.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.taiwan.net.tw/m1.aspx?sNo=0000104</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>507</t>
-  </si>
-  <si>
-    <t>智慧導遊-桃園</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-507.jpg</t>
-  </si>
-  <si>
-    <t>https://tcwang.github.io/TravelGuide-Taoyuan/index.html</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>508</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>智慧導遊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-花東</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-508.jpg</t>
-  </si>
-  <si>
-    <t>https://tcwang.github.io/TravelGuide-EastCoast/index.html</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>509</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>智慧導遊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-離島</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-509.jpg</t>
-  </si>
-  <si>
-    <t>https://tcwang.github.io/TravelGuide-Islands/Index.html</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/AiCity-945-WebInformation-310.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>果汁排行榜</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://guozhivip.com/rank/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/XLK-142-果汁排行榜.jpeg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>311</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>大數據導航</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://hao.199it.com/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>312</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>懶盤搜索</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/XLK-142-lzpan.png</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://lzpan.com/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-1401-News/XLK-142-大數據導航.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>075</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>娛樂資訊</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>影貓電影</t>
@@ -874,6 +838,175 @@
   <si>
     <t>https://ustvgo.tv/</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>501</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上映電影查詢</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-501.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movies.yahoo.com.tw/showtimes</t>
+  </si>
+  <si>
+    <t>502</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>連續劇熱播表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-502.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kan.sogou.com/top/dianshiju/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>503</t>
+  </si>
+  <si>
+    <t>附近景點快搜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-503.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.taiwan.net.tw/m1.aspx?sNo=0000064</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>主題旅遊資訊</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-504.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.taiwan.net.tw/m1.aspx?sNo=0000108</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>藝文活動資訊</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-505.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://event.moc.gov.tw/mp.asp?mp=1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>506</t>
+  </si>
+  <si>
+    <t>地區節慶活動</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-506.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.taiwan.net.tw/m1.aspx?sNo=0000104</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>智慧導遊-桃園</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-507.jpg</t>
+  </si>
+  <si>
+    <t>https://tcwang.github.io/TravelGuide-Taoyuan/index.html</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>508</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>智慧導遊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-花東</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-508.jpg</t>
+  </si>
+  <si>
+    <t>https://tcwang.github.io/TravelGuide-EastCoast/index.html</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>509</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>智慧導遊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-離島</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-509.jpg</t>
+  </si>
+  <si>
+    <t>https://tcwang.github.io/TravelGuide-Islands/Index.html</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1289,8 +1422,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73074AA-F564-AD47-9C34-8D0E67223CF3}">
-  <dimension ref="A1:F48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B673B51-2DC3-1C4D-B17A-38B3CE4B9DB3}">
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -1582,67 +1715,67 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>180</v>
+        <v>62</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>181</v>
+        <v>65</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>183</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>177</v>
+        <v>68</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>178</v>
+      <c r="D16" t="s">
+        <v>69</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>179</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>174</v>
+      <c r="D17" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>176</v>
+        <v>74</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>175</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>63</v>
@@ -1650,19 +1783,19 @@
       <c r="C18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>65</v>
+      <c r="D18" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>63</v>
@@ -1671,18 +1804,18 @@
         <v>64</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>63</v>
@@ -1691,18 +1824,18 @@
         <v>64</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>63</v>
@@ -1711,18 +1844,18 @@
         <v>64</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>63</v>
@@ -1731,18 +1864,18 @@
         <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>63</v>
@@ -1751,556 +1884,682 @@
         <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>173</v>
+        <v>98</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>88</v>
+      <c r="D24" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>94</v>
+        <v>107</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>107</v>
+        <v>119</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>127</v>
+        <v>138</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>131</v>
+        <v>142</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>133</v>
+      <c r="D35" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" s="6" customFormat="1">
-      <c r="A36" s="5" t="s">
-        <v>185</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" s="6" customFormat="1">
-      <c r="A37" s="5" t="s">
-        <v>189</v>
+        <v>101</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" s="6" customFormat="1">
-      <c r="A38" s="5" t="s">
-        <v>193</v>
+        <v>63</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" s="6" customFormat="1">
-      <c r="A39" s="5" t="s">
-        <v>197</v>
+        <v>63</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>200</v>
+        <v>63</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>137</v>
+        <v>63</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>140</v>
+        <v>166</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>142</v>
+        <v>63</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="1" t="s">
-        <v>145</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" s="6" customFormat="1">
+      <c r="A42" s="5" t="s">
+        <v>172</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="1" t="s">
-        <v>149</v>
+        <v>173</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" s="6" customFormat="1">
+      <c r="A43" s="5" t="s">
+        <v>177</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="1" t="s">
-        <v>153</v>
+        <v>173</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" s="6" customFormat="1">
+      <c r="A44" s="5" t="s">
+        <v>181</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="1" t="s">
-        <v>157</v>
+        <v>173</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="6" customFormat="1">
+      <c r="A45" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>164</v>
+        <v>191</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>166</v>
+        <v>173</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>172</v>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{BAA7D95C-6E1A-8F48-8FE7-D2CE1D46802D}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{361ABFA0-65A4-914E-BD0F-DF3377C0C3AB}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{2EB97F1B-948F-004F-A053-CD30DCF44E29}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{2110EB8D-A46B-D046-8C07-4D1F28C4E9ED}"/>
-    <hyperlink ref="F7" r:id="rId5" xr:uid="{33227F7A-229B-8947-B37F-D6A4659EB47C}"/>
-    <hyperlink ref="F12" r:id="rId6" xr:uid="{716339FC-7F12-EA48-9995-7C474D0320D0}"/>
-    <hyperlink ref="F10" r:id="rId7" xr:uid="{F779899C-3F73-3440-A492-1C66F2B620C7}"/>
-    <hyperlink ref="F9" r:id="rId8" xr:uid="{65E521B8-6489-7540-A0B8-ABFC65A2BE99}"/>
-    <hyperlink ref="F11" r:id="rId9" xr:uid="{F14F0F5B-995D-B842-8E4F-1355DFB26170}"/>
-    <hyperlink ref="F18" r:id="rId10" xr:uid="{5000AC10-E9A7-2F48-A2E1-A708430E8FD3}"/>
-    <hyperlink ref="F19" r:id="rId11" xr:uid="{EB22B113-4D72-7647-BB12-A4CDD0E84D0D}"/>
-    <hyperlink ref="F21" r:id="rId12" xr:uid="{522AE814-B103-F34F-9D64-872658CD9973}"/>
-    <hyperlink ref="F22" r:id="rId13" xr:uid="{9647D01F-922A-FD4A-9DDD-5190A1432D17}"/>
-    <hyperlink ref="F24" r:id="rId14" xr:uid="{3ABB1380-024B-F845-A7B5-2AF547CFDE2E}"/>
-    <hyperlink ref="F29" r:id="rId15" xr:uid="{A65C8833-7044-4445-9794-215739B5ADAB}"/>
-    <hyperlink ref="F30" r:id="rId16" xr:uid="{F654D832-5868-E74B-AC72-556BE69299C9}"/>
-    <hyperlink ref="F31" r:id="rId17" xr:uid="{4E4EC6F8-E6E4-D54B-8AA8-5FE15BF5A751}"/>
-    <hyperlink ref="F32" r:id="rId18" xr:uid="{9765A227-82C2-D549-9458-DDC2D3C28D8D}"/>
-    <hyperlink ref="F41" r:id="rId19" xr:uid="{CD3DA3AB-30AB-524E-9120-1075FCEB7656}"/>
-    <hyperlink ref="F42" r:id="rId20" xr:uid="{77D5314A-0EBE-4B47-B3B2-F976C9B41794}"/>
-    <hyperlink ref="F43" r:id="rId21" xr:uid="{CD171E9C-3BA1-2541-8ED8-7E8ADE5E0BBD}"/>
-    <hyperlink ref="F44" r:id="rId22" xr:uid="{066093EC-3EC4-5349-B64C-CAA4B3AD38C2}"/>
-    <hyperlink ref="F45" r:id="rId23" xr:uid="{1B7909EB-3D00-C942-AAE7-00B7E5D828CD}"/>
-    <hyperlink ref="F13" r:id="rId24" xr:uid="{752C52CB-FC5F-B447-84E0-E36801D34DA7}"/>
-    <hyperlink ref="F27" r:id="rId25" xr:uid="{6FFCA69B-21A4-CB47-9C03-B94CB60F3CB0}"/>
-    <hyperlink ref="F34" r:id="rId26" xr:uid="{18492F93-4F5D-E54F-8131-EF4E56BB3753}"/>
-    <hyperlink ref="F46" r:id="rId27" xr:uid="{89CB1C70-DE0E-E64D-B256-D814AA226C99}"/>
-    <hyperlink ref="F47" r:id="rId28" xr:uid="{04F522F7-AD32-DC45-8F1B-7192EBEF625A}"/>
-    <hyperlink ref="F48" r:id="rId29" xr:uid="{72BD642C-EE89-8946-AF0A-11CAD94A0C95}"/>
-    <hyperlink ref="F35" r:id="rId30" xr:uid="{D72923EF-ED37-F140-B006-2328C3703B41}"/>
-    <hyperlink ref="F23" r:id="rId31" xr:uid="{D2F469D1-1983-AD4A-A51E-2E275AEAB5B9}"/>
-    <hyperlink ref="F17" r:id="rId32" xr:uid="{6508207D-BBE9-CA4B-829A-334E053A7F40}"/>
-    <hyperlink ref="F16" r:id="rId33" xr:uid="{48BBCC1A-D008-C145-8EA7-2A1C9A10CFCB}"/>
-    <hyperlink ref="F15" r:id="rId34" xr:uid="{A4A1607A-2169-D04B-A519-2CC1E57426DC}"/>
-    <hyperlink ref="F39" r:id="rId35" xr:uid="{A9B76A01-5C69-2042-B892-8A6CCA8FA194}"/>
-    <hyperlink ref="F37" r:id="rId36" xr:uid="{BC59EB1D-78B5-4541-AFA6-9F643F390499}"/>
-    <hyperlink ref="F38" r:id="rId37" xr:uid="{DCAAB2E2-2A00-E241-934E-979AE7E30648}"/>
-    <hyperlink ref="F36" r:id="rId38" xr:uid="{F00BAE17-5761-C048-9157-F06361A501DD}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{21E5797E-82FD-A647-95ED-E7664C46502A}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{3B0280D6-31C3-234D-B2EB-62AE87D7810E}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{6B9A789A-E6C0-9141-AD41-BAAF52863868}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{0C5F1754-25DF-544B-9218-11C1FCF4FAFB}"/>
+    <hyperlink ref="F7" r:id="rId5" xr:uid="{D2A06155-D711-F045-9EFB-2C59B9B178C6}"/>
+    <hyperlink ref="F12" r:id="rId6" xr:uid="{9950A79B-6DE2-0A4F-9A7B-1D62F53F5C2B}"/>
+    <hyperlink ref="F10" r:id="rId7" xr:uid="{F4552057-BD3D-EC4B-9205-32248C13E9D9}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{0026D146-8C9E-E349-BCAA-0B68896B00A4}"/>
+    <hyperlink ref="F11" r:id="rId9" xr:uid="{D55C31E4-DC25-FD45-BADC-CD9897387815}"/>
+    <hyperlink ref="F24" r:id="rId10" xr:uid="{40F5A1E2-9233-B344-A5FD-D0072A4A1E67}"/>
+    <hyperlink ref="F25" r:id="rId11" xr:uid="{70CD3FB6-EC49-7B40-9DFF-00CECB61A8B5}"/>
+    <hyperlink ref="F27" r:id="rId12" xr:uid="{739A1BD8-161C-3F41-B932-EDE64A600AE0}"/>
+    <hyperlink ref="F28" r:id="rId13" xr:uid="{0F5591C4-0F46-5045-A9DB-ACC59C7FD3B8}"/>
+    <hyperlink ref="F30" r:id="rId14" xr:uid="{69725125-596D-AD44-99CC-49D23CAEE4F7}"/>
+    <hyperlink ref="F35" r:id="rId15" xr:uid="{BEF20E91-1E59-DE4B-9601-A9B0CF0FA094}"/>
+    <hyperlink ref="F36" r:id="rId16" xr:uid="{38F85F45-CD54-B04B-81A7-BDCB96D795EC}"/>
+    <hyperlink ref="F37" r:id="rId17" xr:uid="{E0416B55-74C0-5F43-85ED-8EAB5D7EB740}"/>
+    <hyperlink ref="F38" r:id="rId18" xr:uid="{090E1445-5C27-674D-919E-34D03661F28D}"/>
+    <hyperlink ref="F47" r:id="rId19" xr:uid="{579BBFF6-4B0E-324E-AB82-7D7ADA216703}"/>
+    <hyperlink ref="F48" r:id="rId20" xr:uid="{7AC6A68F-518C-AB46-B7DC-CF4C3510F426}"/>
+    <hyperlink ref="F49" r:id="rId21" xr:uid="{C1197B06-FD24-DF4A-A2A5-79FEDE75CBE8}"/>
+    <hyperlink ref="F50" r:id="rId22" xr:uid="{F623B902-DF2B-7646-9071-59E2ED79A719}"/>
+    <hyperlink ref="F51" r:id="rId23" xr:uid="{44289907-4C21-164C-AC86-F0AEFBE12DFB}"/>
+    <hyperlink ref="F13" r:id="rId24" xr:uid="{D43FDAED-142C-1146-8FB6-7E5E5E3D4205}"/>
+    <hyperlink ref="F33" r:id="rId25" xr:uid="{7778745A-391B-EE4C-8B78-831793B2829E}"/>
+    <hyperlink ref="F40" r:id="rId26" xr:uid="{7E1BA332-C868-764D-AEFA-6B28D8D63746}"/>
+    <hyperlink ref="F52" r:id="rId27" xr:uid="{F2780B09-BFF4-1344-A31F-563D0E324393}"/>
+    <hyperlink ref="F53" r:id="rId28" xr:uid="{D991E7C8-8F02-7B42-A0A1-B5659CED5F39}"/>
+    <hyperlink ref="F54" r:id="rId29" xr:uid="{BDADB215-6D45-9741-9FB8-604F19768D56}"/>
+    <hyperlink ref="F41" r:id="rId30" xr:uid="{ACA13B2C-7853-F346-ADFF-E344976F82B9}"/>
+    <hyperlink ref="F29" r:id="rId31" xr:uid="{356B5AA0-5A52-EF4A-ACB1-B5C583E9D3DE}"/>
+    <hyperlink ref="F23" r:id="rId32" xr:uid="{7D30CE98-1B5D-244F-AA7C-EFE7872BD49B}"/>
+    <hyperlink ref="F22" r:id="rId33" xr:uid="{5B10DCB0-F2EA-034F-BA1E-FE1BA091021A}"/>
+    <hyperlink ref="F21" r:id="rId34" xr:uid="{AFD21F27-EEB9-BF4D-B2B3-F9BDC8F03C51}"/>
+    <hyperlink ref="F45" r:id="rId35" xr:uid="{F4FE5BB7-2E03-6C4B-8A7A-81FB30AAF26D}"/>
+    <hyperlink ref="F43" r:id="rId36" xr:uid="{047ED4DA-0474-AE40-9DEB-4FA7133C4634}"/>
+    <hyperlink ref="F44" r:id="rId37" xr:uid="{181C503C-952F-DC4A-85B6-6354DD3E0E1C}"/>
+    <hyperlink ref="F42" r:id="rId38" xr:uid="{F251423F-8BDF-FF42-B6C0-74A59EFC9E71}"/>
+    <hyperlink ref="F15" r:id="rId39" xr:uid="{5CFF2553-D34B-AA49-BBF4-1143C3540D5C}"/>
+    <hyperlink ref="F16" r:id="rId40" xr:uid="{BEBC1A90-8711-6C4B-BF95-152B262ABEC1}"/>
+    <hyperlink ref="F17" r:id="rId41" xr:uid="{C22D9546-54DB-3B49-80B8-446D98B7CDD6}"/>
+    <hyperlink ref="F18" r:id="rId42" xr:uid="{2205FA23-7B4A-5E41-B430-67A32C4C85AA}"/>
+    <hyperlink ref="F19" r:id="rId43" xr:uid="{6B379F75-A4D4-2B4C-A064-17656CC9BF99}"/>
+    <hyperlink ref="F20" r:id="rId44" xr:uid="{755FBDC3-417D-3449-8BE6-3DE2E66DCD03}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1404-WebInformation.xlsx
+++ b/db/A7XLK-1404-WebInformation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E1C508B-EB7B-BC4F-B04E-A99F1E58C459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1719C08-2A35-0A4C-B398-10D3A70017E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8780" yWindow="10020" windowWidth="27860" windowHeight="16820" xr2:uid="{28C80269-29E6-DF43-8891-366D5E15C1BF}"/>
+    <workbookView xWindow="5540" yWindow="1540" windowWidth="27860" windowHeight="16820" xr2:uid="{28C80269-29E6-DF43-8891-366D5E15C1BF}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="257">
   <si>
     <t>No</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1006,6 +1006,127 @@
   </si>
   <si>
     <t>https://tcwang.github.io/TravelGuide-Islands/Index.html</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>510</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>511</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>512</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>513</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-510.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>獨播庫</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.duboku.tv/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bigdramas.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-511.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>大劇獨播</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wetv.vip/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeTV 付費</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-512.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dramasq.com/cn/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramasQ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-513.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-514.jpeg</t>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-515.jpeg</t>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-516.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.iq.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛奇藝 付費</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://w.mgtv.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>芒果TV 付費</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>影视之家</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.743718.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-945-WebInformation-517.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://v.qq.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>騰訊視頻 付費</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1097,7 +1218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1108,6 +1229,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1423,7 +1546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B673B51-2DC3-1C4D-B17A-38B3CE4B9DB3}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -2295,7 +2418,7 @@
     </row>
     <row r="44" spans="1:6" s="6" customFormat="1">
       <c r="A44" s="5" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>173</v>
@@ -2304,212 +2427,372 @@
         <v>173</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>183</v>
+        <v>230</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="6" customFormat="1">
       <c r="A45" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="6" customFormat="1">
+      <c r="A46" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="6" customFormat="1">
+      <c r="A47" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="6" customFormat="1">
+      <c r="A48" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="6" customFormat="1">
+      <c r="A49" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="6" customFormat="1">
+      <c r="A50" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="6" customFormat="1">
+      <c r="A51" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="6" customFormat="1">
+      <c r="A52" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" s="6" customFormat="1">
+      <c r="A53" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D45" s="6" t="s">
+      <c r="B53" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E53" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F53" s="7" t="s">
         <v>188</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D54" s="4" t="s">
+      <c r="B62" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F62" s="3" t="s">
         <v>224</v>
       </c>
     </row>
@@ -2534,25 +2817,25 @@
     <hyperlink ref="F36" r:id="rId16" xr:uid="{38F85F45-CD54-B04B-81A7-BDCB96D795EC}"/>
     <hyperlink ref="F37" r:id="rId17" xr:uid="{E0416B55-74C0-5F43-85ED-8EAB5D7EB740}"/>
     <hyperlink ref="F38" r:id="rId18" xr:uid="{090E1445-5C27-674D-919E-34D03661F28D}"/>
-    <hyperlink ref="F47" r:id="rId19" xr:uid="{579BBFF6-4B0E-324E-AB82-7D7ADA216703}"/>
-    <hyperlink ref="F48" r:id="rId20" xr:uid="{7AC6A68F-518C-AB46-B7DC-CF4C3510F426}"/>
-    <hyperlink ref="F49" r:id="rId21" xr:uid="{C1197B06-FD24-DF4A-A2A5-79FEDE75CBE8}"/>
-    <hyperlink ref="F50" r:id="rId22" xr:uid="{F623B902-DF2B-7646-9071-59E2ED79A719}"/>
-    <hyperlink ref="F51" r:id="rId23" xr:uid="{44289907-4C21-164C-AC86-F0AEFBE12DFB}"/>
+    <hyperlink ref="F55" r:id="rId19" xr:uid="{579BBFF6-4B0E-324E-AB82-7D7ADA216703}"/>
+    <hyperlink ref="F56" r:id="rId20" xr:uid="{7AC6A68F-518C-AB46-B7DC-CF4C3510F426}"/>
+    <hyperlink ref="F57" r:id="rId21" xr:uid="{C1197B06-FD24-DF4A-A2A5-79FEDE75CBE8}"/>
+    <hyperlink ref="F58" r:id="rId22" xr:uid="{F623B902-DF2B-7646-9071-59E2ED79A719}"/>
+    <hyperlink ref="F59" r:id="rId23" xr:uid="{44289907-4C21-164C-AC86-F0AEFBE12DFB}"/>
     <hyperlink ref="F13" r:id="rId24" xr:uid="{D43FDAED-142C-1146-8FB6-7E5E5E3D4205}"/>
     <hyperlink ref="F33" r:id="rId25" xr:uid="{7778745A-391B-EE4C-8B78-831793B2829E}"/>
     <hyperlink ref="F40" r:id="rId26" xr:uid="{7E1BA332-C868-764D-AEFA-6B28D8D63746}"/>
-    <hyperlink ref="F52" r:id="rId27" xr:uid="{F2780B09-BFF4-1344-A31F-563D0E324393}"/>
-    <hyperlink ref="F53" r:id="rId28" xr:uid="{D991E7C8-8F02-7B42-A0A1-B5659CED5F39}"/>
-    <hyperlink ref="F54" r:id="rId29" xr:uid="{BDADB215-6D45-9741-9FB8-604F19768D56}"/>
+    <hyperlink ref="F60" r:id="rId27" xr:uid="{F2780B09-BFF4-1344-A31F-563D0E324393}"/>
+    <hyperlink ref="F61" r:id="rId28" xr:uid="{D991E7C8-8F02-7B42-A0A1-B5659CED5F39}"/>
+    <hyperlink ref="F62" r:id="rId29" xr:uid="{BDADB215-6D45-9741-9FB8-604F19768D56}"/>
     <hyperlink ref="F41" r:id="rId30" xr:uid="{ACA13B2C-7853-F346-ADFF-E344976F82B9}"/>
     <hyperlink ref="F29" r:id="rId31" xr:uid="{356B5AA0-5A52-EF4A-ACB1-B5C583E9D3DE}"/>
     <hyperlink ref="F23" r:id="rId32" xr:uid="{7D30CE98-1B5D-244F-AA7C-EFE7872BD49B}"/>
     <hyperlink ref="F22" r:id="rId33" xr:uid="{5B10DCB0-F2EA-034F-BA1E-FE1BA091021A}"/>
     <hyperlink ref="F21" r:id="rId34" xr:uid="{AFD21F27-EEB9-BF4D-B2B3-F9BDC8F03C51}"/>
-    <hyperlink ref="F45" r:id="rId35" xr:uid="{F4FE5BB7-2E03-6C4B-8A7A-81FB30AAF26D}"/>
+    <hyperlink ref="F53" r:id="rId35" xr:uid="{F4FE5BB7-2E03-6C4B-8A7A-81FB30AAF26D}"/>
     <hyperlink ref="F43" r:id="rId36" xr:uid="{047ED4DA-0474-AE40-9DEB-4FA7133C4634}"/>
-    <hyperlink ref="F44" r:id="rId37" xr:uid="{181C503C-952F-DC4A-85B6-6354DD3E0E1C}"/>
+    <hyperlink ref="F52" r:id="rId37" xr:uid="{181C503C-952F-DC4A-85B6-6354DD3E0E1C}"/>
     <hyperlink ref="F42" r:id="rId38" xr:uid="{F251423F-8BDF-FF42-B6C0-74A59EFC9E71}"/>
     <hyperlink ref="F15" r:id="rId39" xr:uid="{5CFF2553-D34B-AA49-BBF4-1143C3540D5C}"/>
     <hyperlink ref="F16" r:id="rId40" xr:uid="{BEBC1A90-8711-6C4B-BF95-152B262ABEC1}"/>
@@ -2560,6 +2843,15 @@
     <hyperlink ref="F18" r:id="rId42" xr:uid="{2205FA23-7B4A-5E41-B430-67A32C4C85AA}"/>
     <hyperlink ref="F19" r:id="rId43" xr:uid="{6B379F75-A4D4-2B4C-A064-17656CC9BF99}"/>
     <hyperlink ref="F20" r:id="rId44" xr:uid="{755FBDC3-417D-3449-8BE6-3DE2E66DCD03}"/>
+    <hyperlink ref="F44" r:id="rId45" xr:uid="{F570805D-622E-1148-9CDE-F436A8219D16}"/>
+    <hyperlink ref="F45" r:id="rId46" xr:uid="{57EAE77E-DFBD-D94D-ACEB-12F6BD0D26CD}"/>
+    <hyperlink ref="D46" r:id="rId47" display="https://wetv.vip/" xr:uid="{D80DABCA-3B40-F849-B4A2-5D3DEE333FF5}"/>
+    <hyperlink ref="F46" r:id="rId48" xr:uid="{22A54AAD-7EB2-284E-B86B-252F1474F668}"/>
+    <hyperlink ref="F47" r:id="rId49" xr:uid="{C02A8F73-6256-FA40-8758-3F1DF0B5228A}"/>
+    <hyperlink ref="F48" r:id="rId50" xr:uid="{1BB22238-F30A-0843-876E-9099462E2B60}"/>
+    <hyperlink ref="F49" r:id="rId51" xr:uid="{A4A37100-ABA3-C74B-9AFB-64DD64798FCA}"/>
+    <hyperlink ref="F50" r:id="rId52" xr:uid="{41B84512-8E8D-3746-951C-C7C7DA5964A4}"/>
+    <hyperlink ref="F51" r:id="rId53" xr:uid="{F2F395CA-6986-0F4E-A759-F04361E12603}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1404-WebInformation.xlsx
+++ b/db/A7XLK-1404-WebInformation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1719C08-2A35-0A4C-B398-10D3A70017E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87881AB9-2396-194F-92B5-F5491172DE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5540" yWindow="1540" windowWidth="27860" windowHeight="16820" xr2:uid="{28C80269-29E6-DF43-8891-366D5E15C1BF}"/>
+    <workbookView xWindow="940" yWindow="1180" windowWidth="27860" windowHeight="16820" xr2:uid="{28C80269-29E6-DF43-8891-366D5E15C1BF}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="261">
   <si>
     <t>No</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1128,6 +1128,22 @@
   <si>
     <t>騰訊視頻 付費</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>076</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>泥巴影院</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-1401-News/XLK-142-泥巴.png</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.nbys.tv/index.html</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1546,7 +1562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B673B51-2DC3-1C4D-B17A-38B3CE4B9DB3}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -2378,7 +2394,7 @@
     </row>
     <row r="42" spans="1:6" s="6" customFormat="1">
       <c r="A42" s="5" t="s">
-        <v>172</v>
+        <v>257</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>173</v>
@@ -2387,18 +2403,18 @@
         <v>173</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>176</v>
+        <v>260</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="6" customFormat="1">
       <c r="A43" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>173</v>
@@ -2407,18 +2423,18 @@
         <v>173</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:6" s="6" customFormat="1">
       <c r="A44" s="5" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>173</v>
@@ -2427,18 +2443,18 @@
         <v>173</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>229</v>
+        <v>178</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="6" customFormat="1">
       <c r="A45" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>173</v>
@@ -2447,18 +2463,18 @@
         <v>173</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:6" s="6" customFormat="1">
       <c r="A46" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>173</v>
@@ -2466,19 +2482,19 @@
       <c r="C46" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D46" s="8" t="s">
-        <v>236</v>
+      <c r="D46" s="6" t="s">
+        <v>234</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="6" customFormat="1">
       <c r="A47" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>173</v>
@@ -2486,19 +2502,19 @@
       <c r="C47" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>239</v>
+      <c r="D47" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="6" customFormat="1">
       <c r="A48" s="5" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>173</v>
@@ -2507,18 +2523,18 @@
         <v>173</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="6" customFormat="1">
       <c r="A49" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>173</v>
@@ -2527,18 +2543,18 @@
         <v>173</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="6" customFormat="1">
       <c r="A50" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>173</v>
@@ -2547,18 +2563,18 @@
         <v>173</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="6" customFormat="1">
       <c r="A51" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>173</v>
@@ -2567,18 +2583,18 @@
         <v>173</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="6" customFormat="1">
       <c r="A52" s="5" t="s">
-        <v>181</v>
+        <v>244</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>173</v>
@@ -2586,59 +2602,59 @@
       <c r="C52" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>183</v>
+      <c r="D52" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="6" customFormat="1">
       <c r="A53" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" s="6" customFormat="1">
+      <c r="A54" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D53" s="6" t="s">
+      <c r="B54" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E54" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F54" s="7" t="s">
         <v>188</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>173</v>
@@ -2647,18 +2663,18 @@
         <v>173</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>173</v>
@@ -2667,18 +2683,18 @@
         <v>173</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>173</v>
@@ -2687,18 +2703,18 @@
         <v>173</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>173</v>
@@ -2707,18 +2723,18 @@
         <v>173</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>173</v>
@@ -2727,18 +2743,18 @@
         <v>173</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>173</v>
@@ -2747,18 +2763,18 @@
         <v>173</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>173</v>
@@ -2766,33 +2782,53 @@
       <c r="C61" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>218</v>
+      <c r="D61" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="B63" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F63" s="3" t="s">
         <v>224</v>
       </c>
     </row>
@@ -2817,41 +2853,42 @@
     <hyperlink ref="F36" r:id="rId16" xr:uid="{38F85F45-CD54-B04B-81A7-BDCB96D795EC}"/>
     <hyperlink ref="F37" r:id="rId17" xr:uid="{E0416B55-74C0-5F43-85ED-8EAB5D7EB740}"/>
     <hyperlink ref="F38" r:id="rId18" xr:uid="{090E1445-5C27-674D-919E-34D03661F28D}"/>
-    <hyperlink ref="F55" r:id="rId19" xr:uid="{579BBFF6-4B0E-324E-AB82-7D7ADA216703}"/>
-    <hyperlink ref="F56" r:id="rId20" xr:uid="{7AC6A68F-518C-AB46-B7DC-CF4C3510F426}"/>
-    <hyperlink ref="F57" r:id="rId21" xr:uid="{C1197B06-FD24-DF4A-A2A5-79FEDE75CBE8}"/>
-    <hyperlink ref="F58" r:id="rId22" xr:uid="{F623B902-DF2B-7646-9071-59E2ED79A719}"/>
-    <hyperlink ref="F59" r:id="rId23" xr:uid="{44289907-4C21-164C-AC86-F0AEFBE12DFB}"/>
+    <hyperlink ref="F56" r:id="rId19" xr:uid="{579BBFF6-4B0E-324E-AB82-7D7ADA216703}"/>
+    <hyperlink ref="F57" r:id="rId20" xr:uid="{7AC6A68F-518C-AB46-B7DC-CF4C3510F426}"/>
+    <hyperlink ref="F58" r:id="rId21" xr:uid="{C1197B06-FD24-DF4A-A2A5-79FEDE75CBE8}"/>
+    <hyperlink ref="F59" r:id="rId22" xr:uid="{F623B902-DF2B-7646-9071-59E2ED79A719}"/>
+    <hyperlink ref="F60" r:id="rId23" xr:uid="{44289907-4C21-164C-AC86-F0AEFBE12DFB}"/>
     <hyperlink ref="F13" r:id="rId24" xr:uid="{D43FDAED-142C-1146-8FB6-7E5E5E3D4205}"/>
     <hyperlink ref="F33" r:id="rId25" xr:uid="{7778745A-391B-EE4C-8B78-831793B2829E}"/>
     <hyperlink ref="F40" r:id="rId26" xr:uid="{7E1BA332-C868-764D-AEFA-6B28D8D63746}"/>
-    <hyperlink ref="F60" r:id="rId27" xr:uid="{F2780B09-BFF4-1344-A31F-563D0E324393}"/>
-    <hyperlink ref="F61" r:id="rId28" xr:uid="{D991E7C8-8F02-7B42-A0A1-B5659CED5F39}"/>
-    <hyperlink ref="F62" r:id="rId29" xr:uid="{BDADB215-6D45-9741-9FB8-604F19768D56}"/>
+    <hyperlink ref="F61" r:id="rId27" xr:uid="{F2780B09-BFF4-1344-A31F-563D0E324393}"/>
+    <hyperlink ref="F62" r:id="rId28" xr:uid="{D991E7C8-8F02-7B42-A0A1-B5659CED5F39}"/>
+    <hyperlink ref="F63" r:id="rId29" xr:uid="{BDADB215-6D45-9741-9FB8-604F19768D56}"/>
     <hyperlink ref="F41" r:id="rId30" xr:uid="{ACA13B2C-7853-F346-ADFF-E344976F82B9}"/>
     <hyperlink ref="F29" r:id="rId31" xr:uid="{356B5AA0-5A52-EF4A-ACB1-B5C583E9D3DE}"/>
     <hyperlink ref="F23" r:id="rId32" xr:uid="{7D30CE98-1B5D-244F-AA7C-EFE7872BD49B}"/>
     <hyperlink ref="F22" r:id="rId33" xr:uid="{5B10DCB0-F2EA-034F-BA1E-FE1BA091021A}"/>
     <hyperlink ref="F21" r:id="rId34" xr:uid="{AFD21F27-EEB9-BF4D-B2B3-F9BDC8F03C51}"/>
-    <hyperlink ref="F53" r:id="rId35" xr:uid="{F4FE5BB7-2E03-6C4B-8A7A-81FB30AAF26D}"/>
-    <hyperlink ref="F43" r:id="rId36" xr:uid="{047ED4DA-0474-AE40-9DEB-4FA7133C4634}"/>
-    <hyperlink ref="F52" r:id="rId37" xr:uid="{181C503C-952F-DC4A-85B6-6354DD3E0E1C}"/>
-    <hyperlink ref="F42" r:id="rId38" xr:uid="{F251423F-8BDF-FF42-B6C0-74A59EFC9E71}"/>
+    <hyperlink ref="F54" r:id="rId35" xr:uid="{F4FE5BB7-2E03-6C4B-8A7A-81FB30AAF26D}"/>
+    <hyperlink ref="F44" r:id="rId36" xr:uid="{047ED4DA-0474-AE40-9DEB-4FA7133C4634}"/>
+    <hyperlink ref="F53" r:id="rId37" xr:uid="{181C503C-952F-DC4A-85B6-6354DD3E0E1C}"/>
+    <hyperlink ref="F43" r:id="rId38" xr:uid="{F251423F-8BDF-FF42-B6C0-74A59EFC9E71}"/>
     <hyperlink ref="F15" r:id="rId39" xr:uid="{5CFF2553-D34B-AA49-BBF4-1143C3540D5C}"/>
     <hyperlink ref="F16" r:id="rId40" xr:uid="{BEBC1A90-8711-6C4B-BF95-152B262ABEC1}"/>
     <hyperlink ref="F17" r:id="rId41" xr:uid="{C22D9546-54DB-3B49-80B8-446D98B7CDD6}"/>
     <hyperlink ref="F18" r:id="rId42" xr:uid="{2205FA23-7B4A-5E41-B430-67A32C4C85AA}"/>
     <hyperlink ref="F19" r:id="rId43" xr:uid="{6B379F75-A4D4-2B4C-A064-17656CC9BF99}"/>
     <hyperlink ref="F20" r:id="rId44" xr:uid="{755FBDC3-417D-3449-8BE6-3DE2E66DCD03}"/>
-    <hyperlink ref="F44" r:id="rId45" xr:uid="{F570805D-622E-1148-9CDE-F436A8219D16}"/>
-    <hyperlink ref="F45" r:id="rId46" xr:uid="{57EAE77E-DFBD-D94D-ACEB-12F6BD0D26CD}"/>
-    <hyperlink ref="D46" r:id="rId47" display="https://wetv.vip/" xr:uid="{D80DABCA-3B40-F849-B4A2-5D3DEE333FF5}"/>
-    <hyperlink ref="F46" r:id="rId48" xr:uid="{22A54AAD-7EB2-284E-B86B-252F1474F668}"/>
-    <hyperlink ref="F47" r:id="rId49" xr:uid="{C02A8F73-6256-FA40-8758-3F1DF0B5228A}"/>
-    <hyperlink ref="F48" r:id="rId50" xr:uid="{1BB22238-F30A-0843-876E-9099462E2B60}"/>
-    <hyperlink ref="F49" r:id="rId51" xr:uid="{A4A37100-ABA3-C74B-9AFB-64DD64798FCA}"/>
-    <hyperlink ref="F50" r:id="rId52" xr:uid="{41B84512-8E8D-3746-951C-C7C7DA5964A4}"/>
-    <hyperlink ref="F51" r:id="rId53" xr:uid="{F2F395CA-6986-0F4E-A759-F04361E12603}"/>
+    <hyperlink ref="F45" r:id="rId45" xr:uid="{F570805D-622E-1148-9CDE-F436A8219D16}"/>
+    <hyperlink ref="F46" r:id="rId46" xr:uid="{57EAE77E-DFBD-D94D-ACEB-12F6BD0D26CD}"/>
+    <hyperlink ref="D47" r:id="rId47" display="https://wetv.vip/" xr:uid="{D80DABCA-3B40-F849-B4A2-5D3DEE333FF5}"/>
+    <hyperlink ref="F47" r:id="rId48" xr:uid="{22A54AAD-7EB2-284E-B86B-252F1474F668}"/>
+    <hyperlink ref="F48" r:id="rId49" xr:uid="{C02A8F73-6256-FA40-8758-3F1DF0B5228A}"/>
+    <hyperlink ref="F49" r:id="rId50" xr:uid="{1BB22238-F30A-0843-876E-9099462E2B60}"/>
+    <hyperlink ref="F50" r:id="rId51" xr:uid="{A4A37100-ABA3-C74B-9AFB-64DD64798FCA}"/>
+    <hyperlink ref="F51" r:id="rId52" xr:uid="{41B84512-8E8D-3746-951C-C7C7DA5964A4}"/>
+    <hyperlink ref="F52" r:id="rId53" xr:uid="{F2F395CA-6986-0F4E-A759-F04361E12603}"/>
+    <hyperlink ref="F42" r:id="rId54" xr:uid="{610B2EE1-FBEE-BF47-8DC9-6D6B197A8603}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
